--- a/云平台远程连接接口文档.xlsx
+++ b/云平台远程连接接口文档.xlsx
@@ -959,7 +959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>{"battery_soc":85,"warning_state_one":0,"warning_state_two":0,"left_wheel_speed":120,"right_wheel_speed":118,"mower_height":6,"stamp":1751356800.5}</t>
+          <t>{"battery_soc":85,"warning_state_one":0,"warning_state_two":0,"mower_height":6,"stamp":1751356800.5}</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1210,7 +1210,7 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>left_wheel_speed / right_wheel_speed</t>
+          <t>mower_height</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>左右轮转速</t>
+          <t>刀盘高度反馈档位</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1233,43 +1233,20 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>mower_height</t>
+          <t>stamp</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>number</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>刀盘高度反馈档位</t>
+          <t>Unix秒(double)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>stamp</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Unix秒(double)</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1417,7 +1394,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>订阅 /Mower/position (util/Position)，2Hz节流后上报</t>
+          <t>订阅 /Mower/position (mower_msgs/Position)，2Hz节流后上报</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1434,7 +1411,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>订阅 /vehicle/status、/vehicle/left|right_wheel_speed、/vehicle/mower_height_to_app</t>
+          <t>订阅 /vehicle/status、/vehicle/mower_height_to_app</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">

--- a/云平台远程连接接口文档.xlsx
+++ b/云平台远程连接接口文档.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-MQTT上行数据" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-车端ROS映射" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-安全与联调" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-已删除接口" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +38,11 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -79,12 +85,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1561,4 +1570,222 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>接口</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MQTT主题</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>payload示例</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>取值范围/说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>以下接口已于 2026-09-11 从车端 cloud_bridge 中删除，云平台请勿再使用：</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>视频控制（已删除）</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>mower/{设备ID}/cmd/video</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>{"enable": true, "fps": 5, "width": 640, "height": 480, "bitrate": 800}</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>enable</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>true/false；开启/关闭 SRT 推流</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>fps</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>0.1 ~ 30；推流帧率</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>width / height</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>16~1920 / 16~1080；输出分辨率</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>bitrate</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>100 ~ 8000；H.264 码率 kbps</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>整条 SRT 视频通道（H.264 + MPEG-TS，车端 caller 推流）已随本接口一并移除，车端不再订阅 /camera/image_rect，launch 中 srt_target/video_* 参数均已删除</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>车辆状态已删字段</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>mower/{设备ID}/state/vehicle</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>left_wheel_speed</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>左轮速度（原来自 /vehicle/left_wheel_speed）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>right_wheel_speed</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>右轮速度（原来自 /vehicle/right_wheel_speed）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>